--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Barça.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Barça.xlsx
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>48.2592</v>
+        <v>66.6217</v>
       </c>
       <c r="E2" t="n">
-        <v>34.3085</v>
+        <v>48.1213</v>
       </c>
       <c r="F2" t="n">
-        <v>13.9507</v>
+        <v>18.5005</v>
       </c>
       <c r="G2" t="n">
-        <v>11.3198</v>
+        <v>13.409</v>
       </c>
       <c r="H2" t="n">
-        <v>11.0682</v>
+        <v>15.8438</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2519000000000002</v>
+        <v>-2.4349</v>
       </c>
       <c r="J2" t="n">
-        <v>33.1493</v>
+        <v>40.9958</v>
       </c>
       <c r="K2" t="n">
-        <v>28.8975</v>
+        <v>36.3569</v>
       </c>
       <c r="L2" t="n">
-        <v>4.2517</v>
+        <v>4.639</v>
       </c>
       <c r="M2" t="n">
-        <v>-21.8293</v>
+        <v>-27.5869</v>
       </c>
       <c r="N2" t="n">
-        <v>-17.8296</v>
+        <v>-20.5129</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.999499999999999</v>
+        <v>-7.0738</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.8147</v>
+        <v>0.2275000000000005</v>
       </c>
       <c r="Q2" t="n">
-        <v>-34.9324</v>
+        <v>-40.9739</v>
       </c>
       <c r="R2" t="n">
-        <v>33.1175</v>
+        <v>41.2014</v>
       </c>
       <c r="S2" t="n">
-        <v>23.9644</v>
+        <v>29.377</v>
       </c>
       <c r="T2" t="n">
-        <v>13.4986</v>
+        <v>15.2689</v>
       </c>
       <c r="U2" t="n">
-        <v>10.4663</v>
+        <v>14.1081</v>
       </c>
       <c r="V2" t="n">
-        <v>14.7898</v>
+        <v>23.6078</v>
       </c>
       <c r="W2" t="n">
-        <v>22.5936</v>
+        <v>32.8303</v>
       </c>
       <c r="X2" t="n">
-        <v>-7.8036</v>
+        <v>-9.222200000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>46.73990000000001</v>
+        <v>57.8834</v>
       </c>
       <c r="E3" t="n">
-        <v>29.9919</v>
+        <v>49.1997</v>
       </c>
       <c r="F3" t="n">
-        <v>16.7479</v>
+        <v>8.684099999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>8.779500000000002</v>
+        <v>24.0428</v>
       </c>
       <c r="H3" t="n">
-        <v>5.2239</v>
+        <v>25.9636</v>
       </c>
       <c r="I3" t="n">
-        <v>3.556</v>
+        <v>-1.9203</v>
       </c>
       <c r="J3" t="n">
-        <v>35.0498</v>
+        <v>30.5519</v>
       </c>
       <c r="K3" t="n">
-        <v>25.8342</v>
+        <v>26.791</v>
       </c>
       <c r="L3" t="n">
-        <v>9.215499999999999</v>
+        <v>3.7607</v>
       </c>
       <c r="M3" t="n">
-        <v>-26.27</v>
+        <v>-6.5091</v>
       </c>
       <c r="N3" t="n">
-        <v>-20.6107</v>
+        <v>-0.8274999999999997</v>
       </c>
       <c r="O3" t="n">
-        <v>-5.6593</v>
+        <v>-5.6814</v>
       </c>
       <c r="P3" t="n">
-        <v>18.6004</v>
+        <v>-2.9591</v>
       </c>
       <c r="Q3" t="n">
-        <v>-26.7662</v>
+        <v>-19.5765</v>
       </c>
       <c r="R3" t="n">
-        <v>45.3667</v>
+        <v>16.6173</v>
       </c>
       <c r="S3" t="n">
-        <v>14.134</v>
+        <v>38.6612</v>
       </c>
       <c r="T3" t="n">
-        <v>5.414300000000001</v>
+        <v>29.2639</v>
       </c>
       <c r="U3" t="n">
-        <v>8.720000000000001</v>
+        <v>9.397</v>
       </c>
       <c r="V3" t="n">
-        <v>5.2258</v>
+        <v>-1.861</v>
       </c>
       <c r="W3" t="n">
-        <v>16.2941</v>
+        <v>8.959899999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>-11.0684</v>
+        <v>-10.8209</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>38.065</v>
+        <v>48.8441</v>
       </c>
       <c r="E4" t="n">
-        <v>33.1257</v>
+        <v>29.4918</v>
       </c>
       <c r="F4" t="n">
-        <v>4.9393</v>
+        <v>19.3523</v>
       </c>
       <c r="G4" t="n">
-        <v>15.9639</v>
+        <v>3.3964</v>
       </c>
       <c r="H4" t="n">
-        <v>14.4254</v>
+        <v>11.2291</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5388</v>
+        <v>-7.8329</v>
       </c>
       <c r="J4" t="n">
-        <v>18.9834</v>
+        <v>37.9097</v>
       </c>
       <c r="K4" t="n">
-        <v>15.8861</v>
+        <v>32.3803</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0973</v>
+        <v>5.529599999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.0191</v>
+        <v>-34.5135</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4609</v>
+        <v>-21.1512</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5588</v>
+        <v>-13.3624</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6805000000000002</v>
+        <v>22.308</v>
       </c>
       <c r="Q4" t="n">
-        <v>-12.7028</v>
+        <v>-33.6895</v>
       </c>
       <c r="R4" t="n">
-        <v>12.0223</v>
+        <v>55.9975</v>
       </c>
       <c r="S4" t="n">
-        <v>27.2934</v>
+        <v>16.6969</v>
       </c>
       <c r="T4" t="n">
-        <v>20.7388</v>
+        <v>5.315499999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>6.5546</v>
+        <v>11.3814</v>
       </c>
       <c r="V4" t="n">
-        <v>-4.5123</v>
+        <v>6.442600000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>6.1061</v>
+        <v>19.9558</v>
       </c>
       <c r="X4" t="n">
-        <v>-10.6183</v>
+        <v>-13.5131</v>
       </c>
     </row>
     <row r="5">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>17.8456</v>
+        <v>28.92</v>
       </c>
       <c r="E5" t="n">
-        <v>11.7061</v>
+        <v>20.9078</v>
       </c>
       <c r="F5" t="n">
-        <v>6.139500000000001</v>
+        <v>8.011999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>8.333699999999999</v>
+        <v>12.4056</v>
       </c>
       <c r="H5" t="n">
-        <v>21.5887</v>
+        <v>32.3059</v>
       </c>
       <c r="I5" t="n">
-        <v>-13.2554</v>
+        <v>-19.9006</v>
       </c>
       <c r="J5" t="n">
-        <v>24.8041</v>
+        <v>35.7063</v>
       </c>
       <c r="K5" t="n">
-        <v>30.5285</v>
+        <v>42.7528</v>
       </c>
       <c r="L5" t="n">
-        <v>-5.7241</v>
+        <v>-7.0466</v>
       </c>
       <c r="M5" t="n">
-        <v>-16.4709</v>
+        <v>-23.301</v>
       </c>
       <c r="N5" t="n">
-        <v>-8.9397</v>
+        <v>-10.447</v>
       </c>
       <c r="O5" t="n">
-        <v>-7.530900000000001</v>
+        <v>-12.8539</v>
       </c>
       <c r="P5" t="n">
-        <v>-6.3512</v>
+        <v>-3.869599999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-41.5104</v>
+        <v>-51.9002</v>
       </c>
       <c r="R5" t="n">
-        <v>35.1591</v>
+        <v>48.0304</v>
       </c>
       <c r="S5" t="n">
-        <v>3.9403</v>
+        <v>9.9793</v>
       </c>
       <c r="T5" t="n">
-        <v>-3.2118</v>
+        <v>0.7889000000000004</v>
       </c>
       <c r="U5" t="n">
-        <v>7.1518</v>
+        <v>9.1906</v>
       </c>
       <c r="V5" t="n">
-        <v>11.9229</v>
+        <v>10.4047</v>
       </c>
       <c r="W5" t="n">
-        <v>31.6237</v>
+        <v>36.3127</v>
       </c>
       <c r="X5" t="n">
-        <v>-19.7009</v>
+        <v>-25.908</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>17.1579</v>
+        <v>17.1511</v>
       </c>
       <c r="E6" t="n">
-        <v>10.4665</v>
+        <v>17.6676</v>
       </c>
       <c r="F6" t="n">
-        <v>6.691499999999999</v>
+        <v>-0.5169000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07509999999999906</v>
+        <v>38.441</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.5901</v>
+        <v>-2.4275</v>
       </c>
       <c r="I6" t="n">
-        <v>2.665400000000001</v>
+        <v>40.8688</v>
       </c>
       <c r="J6" t="n">
-        <v>16.5662</v>
+        <v>69.4958</v>
       </c>
       <c r="K6" t="n">
-        <v>9.1069</v>
+        <v>19.7431</v>
       </c>
       <c r="L6" t="n">
-        <v>7.4595</v>
+        <v>49.7524</v>
       </c>
       <c r="M6" t="n">
-        <v>-16.4912</v>
+        <v>-31.0546</v>
       </c>
       <c r="N6" t="n">
-        <v>-11.6969</v>
+        <v>-22.1707</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.7943</v>
+        <v>-8.8841</v>
       </c>
       <c r="P6" t="n">
-        <v>17.4662</v>
+        <v>-1.821000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.9903</v>
+        <v>-57.5909</v>
       </c>
       <c r="R6" t="n">
-        <v>22.4565</v>
+        <v>55.7698</v>
       </c>
       <c r="S6" t="n">
-        <v>6.4302</v>
+        <v>-25.4897</v>
       </c>
       <c r="T6" t="n">
-        <v>-3.1665</v>
+        <v>-23.0513</v>
       </c>
       <c r="U6" t="n">
-        <v>9.5967</v>
+        <v>-2.438</v>
       </c>
       <c r="V6" t="n">
-        <v>-6.8134</v>
+        <v>6.0208</v>
       </c>
       <c r="W6" t="n">
-        <v>2.057</v>
+        <v>28.8145</v>
       </c>
       <c r="X6" t="n">
-        <v>-8.8703</v>
+        <v>-22.7937</v>
       </c>
     </row>
     <row r="7">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>17.1385</v>
+        <v>13.9158</v>
       </c>
       <c r="E7" t="n">
-        <v>7.8204</v>
+        <v>5.281199999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>9.318100000000001</v>
+        <v>8.6342</v>
       </c>
       <c r="G7" t="n">
-        <v>5.3765</v>
+        <v>2.1113</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4225</v>
+        <v>-2.578499999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>6.7992</v>
+        <v>4.6899</v>
       </c>
       <c r="J7" t="n">
-        <v>27.1609</v>
+        <v>26.0612</v>
       </c>
       <c r="K7" t="n">
-        <v>10.8851</v>
+        <v>10.6651</v>
       </c>
       <c r="L7" t="n">
-        <v>16.2758</v>
+        <v>15.3963</v>
       </c>
       <c r="M7" t="n">
-        <v>-21.7847</v>
+        <v>-23.95</v>
       </c>
       <c r="N7" t="n">
-        <v>-12.3077</v>
+        <v>-13.2437</v>
       </c>
       <c r="O7" t="n">
-        <v>-9.477</v>
+        <v>-10.7062</v>
       </c>
       <c r="P7" t="n">
-        <v>3.856200000000001</v>
+        <v>3.6423</v>
       </c>
       <c r="Q7" t="n">
-        <v>-30.6226</v>
+        <v>-31.8686</v>
       </c>
       <c r="R7" t="n">
-        <v>34.4787</v>
+        <v>35.5107</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.387700000000001</v>
+        <v>-3.4011</v>
       </c>
       <c r="T7" t="n">
-        <v>-8.2264</v>
+        <v>-8.6379</v>
       </c>
       <c r="U7" t="n">
-        <v>4.8387</v>
+        <v>5.2374</v>
       </c>
       <c r="V7" t="n">
-        <v>11.2933</v>
+        <v>11.5632</v>
       </c>
       <c r="W7" t="n">
-        <v>19.508</v>
+        <v>19.7265</v>
       </c>
       <c r="X7" t="n">
-        <v>-8.214599999999999</v>
+        <v>-8.163399999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>14.6823</v>
+        <v>11.7499</v>
       </c>
       <c r="E8" t="n">
-        <v>7.1688</v>
+        <v>9.3706</v>
       </c>
       <c r="F8" t="n">
-        <v>7.5134</v>
+        <v>2.379</v>
       </c>
       <c r="G8" t="n">
-        <v>22.812</v>
+        <v>21.1314</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3692</v>
+        <v>8.7926</v>
       </c>
       <c r="I8" t="n">
-        <v>20.4426</v>
+        <v>12.3387</v>
       </c>
       <c r="J8" t="n">
-        <v>33.5949</v>
+        <v>40.226</v>
       </c>
       <c r="K8" t="n">
-        <v>10.2666</v>
+        <v>19.6533</v>
       </c>
       <c r="L8" t="n">
-        <v>23.3282</v>
+        <v>20.5731</v>
       </c>
       <c r="M8" t="n">
-        <v>-10.7828</v>
+        <v>-19.0947</v>
       </c>
       <c r="N8" t="n">
-        <v>-7.8975</v>
+        <v>-10.8604</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.8856</v>
+        <v>-8.234499999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>5.8979</v>
+        <v>5.691</v>
       </c>
       <c r="Q8" t="n">
-        <v>-26.3129</v>
+        <v>-33.4621</v>
       </c>
       <c r="R8" t="n">
-        <v>32.2103</v>
+        <v>39.1529</v>
       </c>
       <c r="S8" t="n">
-        <v>-9.663</v>
+        <v>-11.4285</v>
       </c>
       <c r="T8" t="n">
-        <v>-9.2727</v>
+        <v>-10.4822</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3903999999999999</v>
+        <v>-0.9458999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-4.3643</v>
+        <v>-3.644</v>
       </c>
       <c r="W8" t="n">
-        <v>9.1594</v>
+        <v>13.0888</v>
       </c>
       <c r="X8" t="n">
-        <v>-13.5238</v>
+        <v>-16.7329</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>11.7871</v>
+        <v>11.2775</v>
       </c>
       <c r="E9" t="n">
-        <v>13.1588</v>
+        <v>5.617100000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.371900000000001</v>
+        <v>5.660600000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>7.970999999999999</v>
+        <v>-10.4793</v>
       </c>
       <c r="H9" t="n">
-        <v>5.852</v>
+        <v>-5.894599999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>2.118799999999998</v>
+        <v>-4.5848</v>
       </c>
       <c r="J9" t="n">
-        <v>26.9627</v>
+        <v>12.0671</v>
       </c>
       <c r="K9" t="n">
-        <v>20.3139</v>
+        <v>7.7193</v>
       </c>
       <c r="L9" t="n">
-        <v>6.648900000000001</v>
+        <v>4.3477</v>
       </c>
       <c r="M9" t="n">
-        <v>-18.9915</v>
+        <v>-22.5465</v>
       </c>
       <c r="N9" t="n">
-        <v>-14.4616</v>
+        <v>-13.6136</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.5298</v>
+        <v>-8.933</v>
       </c>
       <c r="P9" t="n">
-        <v>15.8782</v>
+        <v>22.0802</v>
       </c>
       <c r="Q9" t="n">
-        <v>-15.1978</v>
+        <v>-7.511900000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>31.0763</v>
+        <v>29.5922</v>
       </c>
       <c r="S9" t="n">
-        <v>-4.934</v>
+        <v>7.776</v>
       </c>
       <c r="T9" t="n">
-        <v>-3.7801</v>
+        <v>-2.537</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1538</v>
+        <v>10.3132</v>
       </c>
       <c r="V9" t="n">
-        <v>-7.128</v>
+        <v>-8.099600000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>5.1743</v>
+        <v>3.5989</v>
       </c>
       <c r="X9" t="n">
-        <v>-12.3025</v>
+        <v>-11.6986</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. LAPROVITTOLA</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D10" t="n">
-        <v>11.2423</v>
+        <v>10.7015</v>
       </c>
       <c r="E10" t="n">
-        <v>13.3226</v>
+        <v>17.0867</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0807</v>
+        <v>-6.384899999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>28.6982</v>
+        <v>7.388199999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>12.0476</v>
+        <v>4.2256</v>
       </c>
       <c r="I10" t="n">
-        <v>16.6507</v>
+        <v>3.162800000000002</v>
       </c>
       <c r="J10" t="n">
-        <v>36.5543</v>
+        <v>32.9751</v>
       </c>
       <c r="K10" t="n">
-        <v>18.2492</v>
+        <v>21.8361</v>
       </c>
       <c r="L10" t="n">
-        <v>18.3051</v>
+        <v>11.1391</v>
       </c>
       <c r="M10" t="n">
-        <v>-7.856100000000001</v>
+        <v>-25.5874</v>
       </c>
       <c r="N10" t="n">
-        <v>-6.2015</v>
+        <v>-17.6104</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6544</v>
+        <v>-7.976900000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>-8.392800000000001</v>
+        <v>21.1697</v>
       </c>
       <c r="Q10" t="n">
-        <v>-25.8589</v>
+        <v>-17.7554</v>
       </c>
       <c r="R10" t="n">
-        <v>17.4662</v>
+        <v>38.9253</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.973100000000001</v>
+        <v>-6.009600000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.0538</v>
+        <v>-4.5278</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0809</v>
+        <v>-1.4816</v>
       </c>
       <c r="V10" t="n">
-        <v>-5.0906</v>
+        <v>-11.8465</v>
       </c>
       <c r="W10" t="n">
-        <v>7.6811</v>
+        <v>6.394</v>
       </c>
       <c r="X10" t="n">
-        <v>-12.7716</v>
+        <v>-18.2406</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>N. LAPROVITTOLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>8.5108</v>
+        <v>4.4156</v>
       </c>
       <c r="E11" t="n">
-        <v>17.1969</v>
+        <v>9.414899999999998</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.686</v>
+        <v>-4.9992</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7351</v>
+        <v>24.9548</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3116</v>
+        <v>8.8331</v>
       </c>
       <c r="I11" t="n">
-        <v>4.0466</v>
+        <v>16.1216</v>
       </c>
       <c r="J11" t="n">
-        <v>21.6336</v>
+        <v>35.3397</v>
       </c>
       <c r="K11" t="n">
-        <v>9.791100000000002</v>
+        <v>17.0573</v>
       </c>
       <c r="L11" t="n">
-        <v>11.8425</v>
+        <v>18.2821</v>
       </c>
       <c r="M11" t="n">
-        <v>-18.8983</v>
+        <v>-10.3849</v>
       </c>
       <c r="N11" t="n">
-        <v>-11.103</v>
+        <v>-8.2241</v>
       </c>
       <c r="O11" t="n">
-        <v>-7.7953</v>
+        <v>-2.1605</v>
       </c>
       <c r="P11" t="n">
-        <v>16.5589</v>
+        <v>-7.7395</v>
       </c>
       <c r="Q11" t="n">
-        <v>-9.980700000000001</v>
+        <v>-28.2263</v>
       </c>
       <c r="R11" t="n">
-        <v>26.5395</v>
+        <v>20.4869</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8976999999999997</v>
+        <v>-6.6272</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.23</v>
+        <v>-6.5866</v>
       </c>
       <c r="U11" t="n">
-        <v>2.332</v>
+        <v>-0.04050000000000004</v>
       </c>
       <c r="V11" t="n">
-        <v>-9.8855</v>
+        <v>-6.172599999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>8.7738</v>
+        <v>8.888500000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>-18.6594</v>
+        <v>-15.0608</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>4.262899999999998</v>
+        <v>4.410000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>9.725300000000001</v>
+        <v>15.5962</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.462400000000001</v>
+        <v>-11.1861</v>
       </c>
       <c r="G12" t="n">
-        <v>25.8992</v>
+        <v>2.0979</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.7614</v>
+        <v>-1.660900000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>30.6607</v>
+        <v>3.7588</v>
       </c>
       <c r="J12" t="n">
-        <v>52.7829</v>
+        <v>24.0956</v>
       </c>
       <c r="K12" t="n">
-        <v>16.2099</v>
+        <v>11.3923</v>
       </c>
       <c r="L12" t="n">
-        <v>36.5732</v>
+        <v>12.7031</v>
       </c>
       <c r="M12" t="n">
-        <v>-26.8837</v>
+        <v>-21.9979</v>
       </c>
       <c r="N12" t="n">
-        <v>-20.9709</v>
+        <v>-13.0532</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.9126</v>
+        <v>-8.9444</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.2685</v>
+        <v>16.8449</v>
       </c>
       <c r="Q12" t="n">
-        <v>-46.0472</v>
+        <v>-13.4304</v>
       </c>
       <c r="R12" t="n">
-        <v>43.7787</v>
+        <v>30.2752</v>
       </c>
       <c r="S12" t="n">
-        <v>-20.422</v>
+        <v>-1.568</v>
       </c>
       <c r="T12" t="n">
-        <v>-18.1253</v>
+        <v>-3.0258</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.2971</v>
+        <v>1.4578</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0543</v>
+        <v>-12.9646</v>
       </c>
       <c r="W12" t="n">
-        <v>21.1147</v>
+        <v>7.956999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-20.0604</v>
+        <v>-20.9215</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>N. KUSTURICA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0449</v>
+        <v>-1.619100000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>5.7593</v>
+        <v>-0.008599999999999719</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.714</v>
+        <v>-1.6104</v>
       </c>
       <c r="G13" t="n">
-        <v>20.5469</v>
+        <v>-1.2125</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6729000000000002</v>
+        <v>1.6174</v>
       </c>
       <c r="I13" t="n">
-        <v>19.874</v>
+        <v>-2.8299</v>
       </c>
       <c r="J13" t="n">
-        <v>48.488</v>
+        <v>2.0955</v>
       </c>
       <c r="K13" t="n">
-        <v>17.3114</v>
+        <v>3.6155</v>
       </c>
       <c r="L13" t="n">
-        <v>31.1766</v>
+        <v>-1.5202</v>
       </c>
       <c r="M13" t="n">
-        <v>-27.9413</v>
+        <v>-3.3078</v>
       </c>
       <c r="N13" t="n">
-        <v>-16.6385</v>
+        <v>-1.9981</v>
       </c>
       <c r="O13" t="n">
-        <v>-11.3027</v>
+        <v>-1.3098</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.495</v>
+        <v>1.8209</v>
       </c>
       <c r="Q13" t="n">
-        <v>-41.0569</v>
+        <v>-3.6421</v>
       </c>
       <c r="R13" t="n">
-        <v>38.5617</v>
+        <v>5.4631</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.7349</v>
+        <v>3.2312</v>
       </c>
       <c r="T13" t="n">
-        <v>-8.035500000000001</v>
+        <v>1.9965</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6988999999999999</v>
+        <v>1.2344</v>
       </c>
       <c r="V13" t="n">
-        <v>-8.271899999999999</v>
+        <v>-5.4586</v>
       </c>
       <c r="W13" t="n">
-        <v>6.3635</v>
+        <v>-0.4583000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-14.6354</v>
+        <v>-5.0003</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. GONZALEZ</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.5631</v>
+        <v>-2.955999999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.6652</v>
+        <v>3.976799999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1022</v>
+        <v>-6.9333</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3565999999999999</v>
+        <v>19.0911</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2527</v>
+        <v>-0.3913999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1038999999999999</v>
+        <v>19.4824</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6183000000000001</v>
+        <v>48.79</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1732</v>
+        <v>16.1861</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4451000000000001</v>
+        <v>32.604</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9749000000000001</v>
+        <v>-29.6991</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4258</v>
+        <v>-16.5774</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.549</v>
+        <v>-13.1217</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.361</v>
+        <v>-2.959099999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.722</v>
+        <v>-42.3396</v>
       </c>
       <c r="R14" t="n">
-        <v>1.361</v>
+        <v>39.3805</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1546</v>
+        <v>-9.575999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4385</v>
+        <v>-8.796100000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2839</v>
+        <v>-0.7792999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-9.5122</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>6.3226</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-15.8347</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. KUSTURICA</t>
+          <t>D. GONZALEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.6447</v>
+        <v>-4.1908</v>
       </c>
       <c r="E15" t="n">
-        <v>0.06169999999999964</v>
+        <v>-3.6758</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7062</v>
+        <v>-0.5147999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.2096</v>
+        <v>-1.9863</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6263</v>
+        <v>-0.07829999999999998</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.836</v>
+        <v>-1.908</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1566</v>
+        <v>-0.1264</v>
       </c>
       <c r="K15" t="n">
-        <v>3.66</v>
+        <v>0.2241</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.5034</v>
+        <v>-0.3504999999999998</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.3663</v>
+        <v>-1.86</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.0337</v>
+        <v>-0.3025</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3327</v>
+        <v>-1.5575</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8145</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.6293</v>
+        <v>-3.8698</v>
       </c>
       <c r="R15" t="n">
-        <v>5.4439</v>
+        <v>1.821</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2202</v>
+        <v>-0.1558</v>
       </c>
       <c r="T15" t="n">
-        <v>1.984</v>
+        <v>0.3202</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2362</v>
+        <v>-0.476</v>
       </c>
       <c r="V15" t="n">
-        <v>-5.469799999999999</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.4497999999999999</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. NUNEZ</t>
+          <t>S. KEITA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>-6.0583</v>
+        <v>-9.0509</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.1555</v>
+        <v>-3.0973</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0973</v>
+        <v>-5.9537</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.4174</v>
+        <v>-5.0148</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5973000000000001</v>
+        <v>-4.4691</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.82</v>
+        <v>-0.5458999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9545000000000001</v>
+        <v>-1.4345</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9701</v>
+        <v>-2.5143</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.0156</v>
+        <v>1.0798</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.3719</v>
+        <v>-3.5804</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.5674</v>
+        <v>-1.9548</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8044</v>
+        <v>-1.6256</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.4026</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.8977</v>
+        <v>-4.5528</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4952</v>
+        <v>3.8697</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3953</v>
+        <v>4.1154</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.373</v>
+        <v>3.3482</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9778</v>
+        <v>0.7673</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1568</v>
+        <v>-7.4685</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1607</v>
+        <v>-0.4583</v>
       </c>
       <c r="X16" t="n">
-        <v>0.9961</v>
+        <v>-7.0101</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. KEITA</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>-6.1784</v>
+        <v>-11.2505</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.2329</v>
+        <v>-13.3975</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.9456</v>
+        <v>2.1471</v>
       </c>
       <c r="G17" t="n">
-        <v>-5.0014</v>
+        <v>25.8842</v>
       </c>
       <c r="H17" t="n">
-        <v>-5.7719</v>
+        <v>3.873199999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7704</v>
+        <v>22.0108</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.7355</v>
+        <v>35.1018</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.8177</v>
+        <v>11.8746</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0822</v>
+        <v>23.2273</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.266</v>
+        <v>-9.2174</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9543</v>
+        <v>-8.001099999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3117</v>
+        <v>-1.216</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1341</v>
+        <v>-9.333</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2684</v>
+        <v>-41.6567</v>
       </c>
       <c r="R17" t="n">
-        <v>3.4025</v>
+        <v>32.3238</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2448</v>
+        <v>-9.2829</v>
       </c>
       <c r="T17" t="n">
-        <v>3.3813</v>
+        <v>-11.057</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8633999999999999</v>
+        <v>1.7743</v>
       </c>
       <c r="V17" t="n">
-        <v>-6.556</v>
+        <v>-18.5186</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6105</v>
+        <v>4.215199999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>-5.9455</v>
+        <v>-22.7336</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>J. NUNEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>-18.9327</v>
+        <v>-14.7935</v>
       </c>
       <c r="E18" t="n">
-        <v>-17.8375</v>
+        <v>-11.26</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0956</v>
+        <v>-3.5336</v>
       </c>
       <c r="G18" t="n">
-        <v>19.2206</v>
+        <v>-2.5404</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5213</v>
+        <v>3.9183</v>
       </c>
       <c r="I18" t="n">
-        <v>15.6993</v>
+        <v>-6.458699999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>25.893</v>
+        <v>8.1204</v>
       </c>
       <c r="K18" t="n">
-        <v>10.2348</v>
+        <v>8.144600000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>15.6585</v>
+        <v>-0.02399999999999981</v>
       </c>
       <c r="M18" t="n">
-        <v>-6.672499999999999</v>
+        <v>-10.661</v>
       </c>
       <c r="N18" t="n">
-        <v>-6.7134</v>
+        <v>-4.2262</v>
       </c>
       <c r="O18" t="n">
-        <v>0.04119999999999996</v>
+        <v>-6.4349</v>
       </c>
       <c r="P18" t="n">
-        <v>-12.4759</v>
+        <v>-11.1539</v>
       </c>
       <c r="Q18" t="n">
-        <v>-38.1079</v>
+        <v>-20.9422</v>
       </c>
       <c r="R18" t="n">
-        <v>25.632</v>
+        <v>9.7882</v>
       </c>
       <c r="S18" t="n">
-        <v>-7.4748</v>
+        <v>1.9401</v>
       </c>
       <c r="T18" t="n">
-        <v>-8.2898</v>
+        <v>-0.8613000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8146999999999999</v>
+        <v>2.8014</v>
       </c>
       <c r="V18" t="n">
-        <v>-18.2028</v>
+        <v>-3.0391</v>
       </c>
       <c r="W18" t="n">
-        <v>2.6676</v>
+        <v>2.423</v>
       </c>
       <c r="X18" t="n">
-        <v>-20.8703</v>
+        <v>-5.462199999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D19" t="n">
-        <v>202.3592</v>
+        <v>232.0298</v>
       </c>
       <c r="E19" t="n">
-        <v>165.9214</v>
+        <v>200.2925</v>
       </c>
       <c r="F19" t="n">
-        <v>36.43750000000001</v>
+        <v>31.7369</v>
       </c>
       <c r="G19" t="n">
-        <v>167.7465</v>
+        <v>173.1204</v>
       </c>
       <c r="H19" t="n">
-        <v>61.688</v>
+        <v>99.10230000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>106.0591</v>
+        <v>74.01780000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>402.6170000000001</v>
+        <v>477.971</v>
       </c>
       <c r="K19" t="n">
-        <v>225.5008</v>
+        <v>283.8781</v>
       </c>
       <c r="L19" t="n">
-        <v>177.117</v>
+        <v>194.0929</v>
       </c>
       <c r="M19" t="n">
-        <v>-234.8705</v>
+        <v>-304.8522</v>
       </c>
       <c r="N19" t="n">
-        <v>-163.8131</v>
+        <v>-184.7748</v>
       </c>
       <c r="O19" t="n">
-        <v>-71.0568</v>
+        <v>-120.0766</v>
       </c>
       <c r="P19" t="n">
-        <v>41.96420000000001</v>
+        <v>51.2177</v>
       </c>
       <c r="Q19" t="n">
-        <v>-368.6043999999999</v>
+        <v>-452.9889</v>
       </c>
       <c r="R19" t="n">
-        <v>410.5681</v>
+        <v>504.2058999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>23.49939999999999</v>
+        <v>38.2383</v>
       </c>
       <c r="T19" t="n">
-        <v>-26.3094</v>
+        <v>-23.26090000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>49.809</v>
+        <v>61.50160000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-30.8517</v>
+        <v>-30.5462</v>
       </c>
       <c r="W19" t="n">
-        <v>158.2173</v>
+        <v>198.5711</v>
       </c>
       <c r="X19" t="n">
-        <v>-189.0689</v>
+        <v>-229.1166</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Barça.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Barça.xlsx
@@ -565,13 +565,13 @@
         <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>66.6217</v>
+        <v>48.8675</v>
       </c>
       <c r="E2" t="n">
-        <v>48.1213</v>
+        <v>35.413</v>
       </c>
       <c r="F2" t="n">
-        <v>18.5005</v>
+        <v>13.4546</v>
       </c>
       <c r="G2" t="n">
         <v>13.409</v>
@@ -610,13 +610,13 @@
         <v>41.2014</v>
       </c>
       <c r="S2" t="n">
-        <v>29.377</v>
+        <v>11.6228</v>
       </c>
       <c r="T2" t="n">
-        <v>15.2689</v>
+        <v>2.5607</v>
       </c>
       <c r="U2" t="n">
-        <v>14.1081</v>
+        <v>9.0627</v>
       </c>
       <c r="V2" t="n">
         <v>23.6078</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>57.8834</v>
+        <v>41.4828</v>
       </c>
       <c r="E3" t="n">
-        <v>49.1997</v>
+        <v>25.3533</v>
       </c>
       <c r="F3" t="n">
-        <v>8.684099999999999</v>
+        <v>16.1293</v>
       </c>
       <c r="G3" t="n">
-        <v>24.0428</v>
+        <v>3.3964</v>
       </c>
       <c r="H3" t="n">
-        <v>25.9636</v>
+        <v>11.2291</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.9203</v>
+        <v>-7.8329</v>
       </c>
       <c r="J3" t="n">
-        <v>30.5519</v>
+        <v>37.9097</v>
       </c>
       <c r="K3" t="n">
-        <v>26.791</v>
+        <v>32.3803</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7607</v>
+        <v>5.529599999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-6.5091</v>
+        <v>-34.5135</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8274999999999997</v>
+        <v>-21.1512</v>
       </c>
       <c r="O3" t="n">
-        <v>-5.6814</v>
+        <v>-13.3624</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.9591</v>
+        <v>22.308</v>
       </c>
       <c r="Q3" t="n">
-        <v>-19.5765</v>
+        <v>-33.6895</v>
       </c>
       <c r="R3" t="n">
-        <v>16.6173</v>
+        <v>55.9975</v>
       </c>
       <c r="S3" t="n">
-        <v>38.6612</v>
+        <v>9.335599999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>29.2639</v>
+        <v>1.1772</v>
       </c>
       <c r="U3" t="n">
-        <v>9.397</v>
+        <v>8.1584</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.861</v>
+        <v>6.442600000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>8.959899999999999</v>
+        <v>19.9558</v>
       </c>
       <c r="X3" t="n">
-        <v>-10.8209</v>
+        <v>-13.5131</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>48.8441</v>
+        <v>38.6585</v>
       </c>
       <c r="E4" t="n">
-        <v>29.4918</v>
+        <v>31.4745</v>
       </c>
       <c r="F4" t="n">
-        <v>19.3523</v>
+        <v>7.1839</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3964</v>
+        <v>24.0428</v>
       </c>
       <c r="H4" t="n">
-        <v>11.2291</v>
+        <v>25.9636</v>
       </c>
       <c r="I4" t="n">
-        <v>-7.8329</v>
+        <v>-1.9203</v>
       </c>
       <c r="J4" t="n">
-        <v>37.9097</v>
+        <v>30.5519</v>
       </c>
       <c r="K4" t="n">
-        <v>32.3803</v>
+        <v>26.791</v>
       </c>
       <c r="L4" t="n">
-        <v>5.529599999999999</v>
+        <v>3.7607</v>
       </c>
       <c r="M4" t="n">
-        <v>-34.5135</v>
+        <v>-6.5091</v>
       </c>
       <c r="N4" t="n">
-        <v>-21.1512</v>
+        <v>-0.8274999999999997</v>
       </c>
       <c r="O4" t="n">
-        <v>-13.3624</v>
+        <v>-5.6814</v>
       </c>
       <c r="P4" t="n">
-        <v>22.308</v>
+        <v>-2.9591</v>
       </c>
       <c r="Q4" t="n">
-        <v>-33.6895</v>
+        <v>-19.5765</v>
       </c>
       <c r="R4" t="n">
-        <v>55.9975</v>
+        <v>16.6173</v>
       </c>
       <c r="S4" t="n">
-        <v>16.6969</v>
+        <v>19.4359</v>
       </c>
       <c r="T4" t="n">
-        <v>5.315499999999999</v>
+        <v>11.5392</v>
       </c>
       <c r="U4" t="n">
-        <v>11.3814</v>
+        <v>7.8967</v>
       </c>
       <c r="V4" t="n">
-        <v>6.442600000000001</v>
+        <v>-1.861</v>
       </c>
       <c r="W4" t="n">
-        <v>19.9558</v>
+        <v>8.959899999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>-13.5131</v>
+        <v>-10.8209</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>28.92</v>
+        <v>37.4193</v>
       </c>
       <c r="E5" t="n">
-        <v>20.9078</v>
+        <v>31.3661</v>
       </c>
       <c r="F5" t="n">
-        <v>8.011999999999999</v>
+        <v>6.053099999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>12.4056</v>
+        <v>38.441</v>
       </c>
       <c r="H5" t="n">
-        <v>32.3059</v>
+        <v>-2.4275</v>
       </c>
       <c r="I5" t="n">
-        <v>-19.9006</v>
+        <v>40.8688</v>
       </c>
       <c r="J5" t="n">
-        <v>35.7063</v>
+        <v>69.4958</v>
       </c>
       <c r="K5" t="n">
-        <v>42.7528</v>
+        <v>19.7431</v>
       </c>
       <c r="L5" t="n">
-        <v>-7.0466</v>
+        <v>49.7524</v>
       </c>
       <c r="M5" t="n">
-        <v>-23.301</v>
+        <v>-31.0546</v>
       </c>
       <c r="N5" t="n">
-        <v>-10.447</v>
+        <v>-22.1707</v>
       </c>
       <c r="O5" t="n">
-        <v>-12.8539</v>
+        <v>-8.8841</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.869599999999999</v>
+        <v>-1.821000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>-51.9002</v>
+        <v>-57.5909</v>
       </c>
       <c r="R5" t="n">
-        <v>48.0304</v>
+        <v>55.7698</v>
       </c>
       <c r="S5" t="n">
-        <v>9.9793</v>
+        <v>-5.2218</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7889000000000004</v>
+        <v>-9.3536</v>
       </c>
       <c r="U5" t="n">
-        <v>9.1906</v>
+        <v>4.1319</v>
       </c>
       <c r="V5" t="n">
-        <v>10.4047</v>
+        <v>6.0208</v>
       </c>
       <c r="W5" t="n">
-        <v>36.3127</v>
+        <v>28.8145</v>
       </c>
       <c r="X5" t="n">
-        <v>-25.908</v>
+        <v>-22.7937</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>17.1511</v>
+        <v>27.6449</v>
       </c>
       <c r="E6" t="n">
-        <v>17.6676</v>
+        <v>19.3755</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5169000000000001</v>
+        <v>8.2697</v>
       </c>
       <c r="G6" t="n">
-        <v>38.441</v>
+        <v>12.4056</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.4275</v>
+        <v>32.3059</v>
       </c>
       <c r="I6" t="n">
-        <v>40.8688</v>
+        <v>-19.9006</v>
       </c>
       <c r="J6" t="n">
-        <v>69.4958</v>
+        <v>35.7063</v>
       </c>
       <c r="K6" t="n">
-        <v>19.7431</v>
+        <v>42.7528</v>
       </c>
       <c r="L6" t="n">
-        <v>49.7524</v>
+        <v>-7.0466</v>
       </c>
       <c r="M6" t="n">
-        <v>-31.0546</v>
+        <v>-23.301</v>
       </c>
       <c r="N6" t="n">
-        <v>-22.1707</v>
+        <v>-10.447</v>
       </c>
       <c r="O6" t="n">
-        <v>-8.8841</v>
+        <v>-12.8539</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.821000000000001</v>
+        <v>-3.869599999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-57.5909</v>
+        <v>-51.9002</v>
       </c>
       <c r="R6" t="n">
-        <v>55.7698</v>
+        <v>48.0304</v>
       </c>
       <c r="S6" t="n">
-        <v>-25.4897</v>
+        <v>8.704700000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-23.0513</v>
+        <v>-0.7436999999999998</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.438</v>
+        <v>9.448499999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>6.0208</v>
+        <v>10.4047</v>
       </c>
       <c r="W6" t="n">
-        <v>28.8145</v>
+        <v>36.3127</v>
       </c>
       <c r="X6" t="n">
-        <v>-22.7937</v>
+        <v>-25.908</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>13.9158</v>
+        <v>22.4464</v>
       </c>
       <c r="E7" t="n">
-        <v>5.281199999999999</v>
+        <v>15.516</v>
       </c>
       <c r="F7" t="n">
-        <v>8.6342</v>
+        <v>6.9305</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1113</v>
+        <v>21.1314</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.578499999999999</v>
+        <v>8.7926</v>
       </c>
       <c r="I7" t="n">
-        <v>4.6899</v>
+        <v>12.3387</v>
       </c>
       <c r="J7" t="n">
-        <v>26.0612</v>
+        <v>40.226</v>
       </c>
       <c r="K7" t="n">
-        <v>10.6651</v>
+        <v>19.6533</v>
       </c>
       <c r="L7" t="n">
-        <v>15.3963</v>
+        <v>20.5731</v>
       </c>
       <c r="M7" t="n">
-        <v>-23.95</v>
+        <v>-19.0947</v>
       </c>
       <c r="N7" t="n">
-        <v>-13.2437</v>
+        <v>-10.8604</v>
       </c>
       <c r="O7" t="n">
-        <v>-10.7062</v>
+        <v>-8.234499999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>3.6423</v>
+        <v>5.691</v>
       </c>
       <c r="Q7" t="n">
-        <v>-31.8686</v>
+        <v>-33.4621</v>
       </c>
       <c r="R7" t="n">
-        <v>35.5107</v>
+        <v>39.1529</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.4011</v>
+        <v>-0.7314000000000003</v>
       </c>
       <c r="T7" t="n">
-        <v>-8.6379</v>
+        <v>-4.3369</v>
       </c>
       <c r="U7" t="n">
-        <v>5.2374</v>
+        <v>3.6053</v>
       </c>
       <c r="V7" t="n">
-        <v>11.5632</v>
+        <v>-3.644</v>
       </c>
       <c r="W7" t="n">
-        <v>19.7265</v>
+        <v>13.0888</v>
       </c>
       <c r="X7" t="n">
-        <v>-8.163399999999999</v>
+        <v>-16.7329</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D8" t="n">
-        <v>11.7499</v>
+        <v>18.7892</v>
       </c>
       <c r="E8" t="n">
-        <v>9.3706</v>
+        <v>20.7447</v>
       </c>
       <c r="F8" t="n">
-        <v>2.379</v>
+        <v>-1.955299999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>21.1314</v>
+        <v>7.388199999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>8.7926</v>
+        <v>4.2256</v>
       </c>
       <c r="I8" t="n">
-        <v>12.3387</v>
+        <v>3.162800000000002</v>
       </c>
       <c r="J8" t="n">
-        <v>40.226</v>
+        <v>32.9751</v>
       </c>
       <c r="K8" t="n">
-        <v>19.6533</v>
+        <v>21.8361</v>
       </c>
       <c r="L8" t="n">
-        <v>20.5731</v>
+        <v>11.1391</v>
       </c>
       <c r="M8" t="n">
-        <v>-19.0947</v>
+        <v>-25.5874</v>
       </c>
       <c r="N8" t="n">
-        <v>-10.8604</v>
+        <v>-17.6104</v>
       </c>
       <c r="O8" t="n">
-        <v>-8.234499999999999</v>
+        <v>-7.976900000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>5.691</v>
+        <v>21.1697</v>
       </c>
       <c r="Q8" t="n">
-        <v>-33.4621</v>
+        <v>-17.7554</v>
       </c>
       <c r="R8" t="n">
-        <v>39.1529</v>
+        <v>38.9253</v>
       </c>
       <c r="S8" t="n">
-        <v>-11.4285</v>
+        <v>2.0779</v>
       </c>
       <c r="T8" t="n">
-        <v>-10.4822</v>
+        <v>-0.8694000000000002</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9458999999999999</v>
+        <v>2.9473</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.644</v>
+        <v>-11.8465</v>
       </c>
       <c r="W8" t="n">
-        <v>13.0888</v>
+        <v>6.394</v>
       </c>
       <c r="X8" t="n">
-        <v>-16.7329</v>
+        <v>-18.2406</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" t="n">
-        <v>11.2775</v>
+        <v>16.5826</v>
       </c>
       <c r="E9" t="n">
-        <v>5.617100000000001</v>
+        <v>8.946199999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>5.660600000000001</v>
+        <v>7.6363</v>
       </c>
       <c r="G9" t="n">
-        <v>-10.4793</v>
+        <v>2.1113</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.894599999999999</v>
+        <v>-2.578499999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.5848</v>
+        <v>4.6899</v>
       </c>
       <c r="J9" t="n">
-        <v>12.0671</v>
+        <v>26.0612</v>
       </c>
       <c r="K9" t="n">
-        <v>7.7193</v>
+        <v>10.6651</v>
       </c>
       <c r="L9" t="n">
-        <v>4.3477</v>
+        <v>15.3963</v>
       </c>
       <c r="M9" t="n">
-        <v>-22.5465</v>
+        <v>-23.95</v>
       </c>
       <c r="N9" t="n">
-        <v>-13.6136</v>
+        <v>-13.2437</v>
       </c>
       <c r="O9" t="n">
-        <v>-8.933</v>
+        <v>-10.7062</v>
       </c>
       <c r="P9" t="n">
-        <v>22.0802</v>
+        <v>3.6423</v>
       </c>
       <c r="Q9" t="n">
-        <v>-7.511900000000001</v>
+        <v>-31.8686</v>
       </c>
       <c r="R9" t="n">
-        <v>29.5922</v>
+        <v>35.5107</v>
       </c>
       <c r="S9" t="n">
-        <v>7.776</v>
+        <v>-0.7343000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.537</v>
+        <v>-4.9734</v>
       </c>
       <c r="U9" t="n">
-        <v>10.3132</v>
+        <v>4.239100000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-8.099600000000001</v>
+        <v>11.5632</v>
       </c>
       <c r="W9" t="n">
-        <v>3.5989</v>
+        <v>19.7265</v>
       </c>
       <c r="X9" t="n">
-        <v>-11.6986</v>
+        <v>-8.163399999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>10.7015</v>
+        <v>12.4436</v>
       </c>
       <c r="E10" t="n">
-        <v>17.0867</v>
+        <v>8.1882</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.384899999999999</v>
+        <v>4.255600000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>7.388199999999999</v>
+        <v>-10.4793</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2256</v>
+        <v>-5.894599999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>3.162800000000002</v>
+        <v>-4.5848</v>
       </c>
       <c r="J10" t="n">
-        <v>32.9751</v>
+        <v>12.0671</v>
       </c>
       <c r="K10" t="n">
-        <v>21.8361</v>
+        <v>7.7193</v>
       </c>
       <c r="L10" t="n">
-        <v>11.1391</v>
+        <v>4.3477</v>
       </c>
       <c r="M10" t="n">
-        <v>-25.5874</v>
+        <v>-22.5465</v>
       </c>
       <c r="N10" t="n">
-        <v>-17.6104</v>
+        <v>-13.6136</v>
       </c>
       <c r="O10" t="n">
-        <v>-7.976900000000001</v>
+        <v>-8.933</v>
       </c>
       <c r="P10" t="n">
-        <v>21.1697</v>
+        <v>22.0802</v>
       </c>
       <c r="Q10" t="n">
-        <v>-17.7554</v>
+        <v>-7.511900000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>38.9253</v>
+        <v>29.5922</v>
       </c>
       <c r="S10" t="n">
-        <v>-6.009600000000001</v>
+        <v>8.942399999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-4.5278</v>
+        <v>0.03420000000000006</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.4816</v>
+        <v>8.9087</v>
       </c>
       <c r="V10" t="n">
-        <v>-11.8465</v>
+        <v>-8.099600000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>6.394</v>
+        <v>3.5989</v>
       </c>
       <c r="X10" t="n">
-        <v>-18.2406</v>
+        <v>-11.6986</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>4.4156</v>
+        <v>11.1295</v>
       </c>
       <c r="E11" t="n">
-        <v>9.414899999999998</v>
+        <v>13.742</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.9992</v>
+        <v>-2.6121</v>
       </c>
       <c r="G11" t="n">
         <v>24.9548</v>
@@ -1312,13 +1312,13 @@
         <v>20.4869</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.6272</v>
+        <v>0.08689999999999992</v>
       </c>
       <c r="T11" t="n">
-        <v>-6.5866</v>
+        <v>-2.2598</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.04050000000000004</v>
+        <v>2.3467</v>
       </c>
       <c r="V11" t="n">
         <v>-6.172599999999999</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>4.410000000000001</v>
+        <v>3.7157</v>
       </c>
       <c r="E12" t="n">
-        <v>15.5962</v>
+        <v>9.2026</v>
       </c>
       <c r="F12" t="n">
-        <v>-11.1861</v>
+        <v>-5.4871</v>
       </c>
       <c r="G12" t="n">
-        <v>2.0979</v>
+        <v>19.0911</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.660900000000001</v>
+        <v>-0.3913999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>3.7588</v>
+        <v>19.4824</v>
       </c>
       <c r="J12" t="n">
-        <v>24.0956</v>
+        <v>48.79</v>
       </c>
       <c r="K12" t="n">
-        <v>11.3923</v>
+        <v>16.1861</v>
       </c>
       <c r="L12" t="n">
-        <v>12.7031</v>
+        <v>32.604</v>
       </c>
       <c r="M12" t="n">
-        <v>-21.9979</v>
+        <v>-29.6991</v>
       </c>
       <c r="N12" t="n">
-        <v>-13.0532</v>
+        <v>-16.5774</v>
       </c>
       <c r="O12" t="n">
-        <v>-8.9444</v>
+        <v>-13.1217</v>
       </c>
       <c r="P12" t="n">
-        <v>16.8449</v>
+        <v>-2.959099999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.4304</v>
+        <v>-42.3396</v>
       </c>
       <c r="R12" t="n">
-        <v>30.2752</v>
+        <v>39.3805</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.568</v>
+        <v>-2.9038</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.0258</v>
+        <v>-3.5704</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4578</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-12.9646</v>
+        <v>-9.5122</v>
       </c>
       <c r="W12" t="n">
-        <v>7.956999999999999</v>
+        <v>6.3226</v>
       </c>
       <c r="X12" t="n">
-        <v>-20.9215</v>
+        <v>-15.8347</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N. KUSTURICA</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.619100000000001</v>
+        <v>3.002800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.008599999999999719</v>
+        <v>-3.670800000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6104</v>
+        <v>6.6735</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.2125</v>
+        <v>25.8842</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6174</v>
+        <v>3.873199999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.8299</v>
+        <v>22.0108</v>
       </c>
       <c r="J13" t="n">
-        <v>2.0955</v>
+        <v>35.1018</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6155</v>
+        <v>11.8746</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.5202</v>
+        <v>23.2273</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.3078</v>
+        <v>-9.2174</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.9981</v>
+        <v>-8.001099999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3098</v>
+        <v>-1.216</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8209</v>
+        <v>-9.333</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.6421</v>
+        <v>-41.6567</v>
       </c>
       <c r="R13" t="n">
-        <v>5.4631</v>
+        <v>32.3238</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2312</v>
+        <v>4.9702</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9965</v>
+        <v>-1.3309</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2344</v>
+        <v>6.301</v>
       </c>
       <c r="V13" t="n">
-        <v>-5.4586</v>
+        <v>-18.5186</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.4583000000000001</v>
+        <v>4.215199999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.0003</v>
+        <v>-22.7336</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.955999999999998</v>
+        <v>2.0933</v>
       </c>
       <c r="E14" t="n">
-        <v>3.976799999999999</v>
+        <v>13.2136</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.9333</v>
+        <v>-11.1201</v>
       </c>
       <c r="G14" t="n">
-        <v>19.0911</v>
+        <v>2.0979</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3913999999999999</v>
+        <v>-1.660900000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>19.4824</v>
+        <v>3.7588</v>
       </c>
       <c r="J14" t="n">
-        <v>48.79</v>
+        <v>24.0956</v>
       </c>
       <c r="K14" t="n">
-        <v>16.1861</v>
+        <v>11.3923</v>
       </c>
       <c r="L14" t="n">
-        <v>32.604</v>
+        <v>12.7031</v>
       </c>
       <c r="M14" t="n">
-        <v>-29.6991</v>
+        <v>-21.9979</v>
       </c>
       <c r="N14" t="n">
-        <v>-16.5774</v>
+        <v>-13.0532</v>
       </c>
       <c r="O14" t="n">
-        <v>-13.1217</v>
+        <v>-8.9444</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.959099999999999</v>
+        <v>16.8449</v>
       </c>
       <c r="Q14" t="n">
-        <v>-42.3396</v>
+        <v>-13.4304</v>
       </c>
       <c r="R14" t="n">
-        <v>39.3805</v>
+        <v>30.2752</v>
       </c>
       <c r="S14" t="n">
-        <v>-9.575999999999999</v>
+        <v>-3.8845</v>
       </c>
       <c r="T14" t="n">
-        <v>-8.796100000000001</v>
+        <v>-5.4088</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7792999999999999</v>
+        <v>1.5242</v>
       </c>
       <c r="V14" t="n">
-        <v>-9.5122</v>
+        <v>-12.9646</v>
       </c>
       <c r="W14" t="n">
-        <v>6.3226</v>
+        <v>7.956999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-15.8347</v>
+        <v>-20.9215</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. GONZALEZ</t>
+          <t>N. KUSTURICA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.1908</v>
+        <v>-3.148600000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.6758</v>
+        <v>-1.0049</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5147999999999999</v>
+        <v>-2.143699999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.9863</v>
+        <v>-1.2125</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.07829999999999998</v>
+        <v>1.6174</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.908</v>
+        <v>-2.8299</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1264</v>
+        <v>2.0955</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2241</v>
+        <v>3.6155</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.3504999999999998</v>
+        <v>-1.5202</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.86</v>
+        <v>-3.3078</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3025</v>
+        <v>-1.9981</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.5575</v>
+        <v>-1.3098</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.0487</v>
+        <v>1.8209</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.8698</v>
+        <v>-3.6421</v>
       </c>
       <c r="R15" t="n">
-        <v>1.821</v>
+        <v>5.4631</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1558</v>
+        <v>1.7015</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3202</v>
+        <v>1.0002</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.476</v>
+        <v>0.7011999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-5.4586</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.4583000000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-5.0003</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. KEITA</t>
+          <t>D. GONZALEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>-9.0509</v>
+        <v>-3.769</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.0973</v>
+        <v>-3.7246</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.9537</v>
+        <v>-0.04429999999999998</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.0148</v>
+        <v>-1.9863</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.4691</v>
+        <v>-0.07829999999999998</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5458999999999999</v>
+        <v>-1.908</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.4345</v>
+        <v>-0.1264</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.5143</v>
+        <v>0.2241</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0798</v>
+        <v>-0.3504999999999998</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.5804</v>
+        <v>-1.86</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.9548</v>
+        <v>-0.3025</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6256</v>
+        <v>-1.5575</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6829</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.5528</v>
+        <v>-3.8698</v>
       </c>
       <c r="R16" t="n">
-        <v>3.8697</v>
+        <v>1.821</v>
       </c>
       <c r="S16" t="n">
-        <v>4.1154</v>
+        <v>0.266</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3482</v>
+        <v>0.2714</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7673</v>
+        <v>-0.005500000000000005</v>
       </c>
       <c r="V16" t="n">
-        <v>-7.4685</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.4583</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-7.0101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>S. KEITA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>-11.2505</v>
+        <v>-10.8298</v>
       </c>
       <c r="E17" t="n">
-        <v>-13.3975</v>
+        <v>-4.9715</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1471</v>
+        <v>-5.8584</v>
       </c>
       <c r="G17" t="n">
-        <v>25.8842</v>
+        <v>-5.0148</v>
       </c>
       <c r="H17" t="n">
-        <v>3.873199999999999</v>
+        <v>-4.4691</v>
       </c>
       <c r="I17" t="n">
-        <v>22.0108</v>
+        <v>-0.5458999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>35.1018</v>
+        <v>-1.4345</v>
       </c>
       <c r="K17" t="n">
-        <v>11.8746</v>
+        <v>-2.5143</v>
       </c>
       <c r="L17" t="n">
-        <v>23.2273</v>
+        <v>1.0798</v>
       </c>
       <c r="M17" t="n">
-        <v>-9.2174</v>
+        <v>-3.5804</v>
       </c>
       <c r="N17" t="n">
-        <v>-8.001099999999999</v>
+        <v>-1.9548</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.216</v>
+        <v>-1.6256</v>
       </c>
       <c r="P17" t="n">
-        <v>-9.333</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-41.6567</v>
+        <v>-4.5528</v>
       </c>
       <c r="R17" t="n">
-        <v>32.3238</v>
+        <v>3.8697</v>
       </c>
       <c r="S17" t="n">
-        <v>-9.2829</v>
+        <v>2.3365</v>
       </c>
       <c r="T17" t="n">
-        <v>-11.057</v>
+        <v>1.4739</v>
       </c>
       <c r="U17" t="n">
-        <v>1.7743</v>
+        <v>0.8625</v>
       </c>
       <c r="V17" t="n">
-        <v>-18.5186</v>
+        <v>-7.4685</v>
       </c>
       <c r="W17" t="n">
-        <v>4.215199999999999</v>
+        <v>-0.4583</v>
       </c>
       <c r="X17" t="n">
-        <v>-22.7336</v>
+        <v>-7.0101</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>-14.7935</v>
+        <v>-14.2906</v>
       </c>
       <c r="E18" t="n">
-        <v>-11.26</v>
+        <v>-10.5074</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.5336</v>
+        <v>-3.7832</v>
       </c>
       <c r="G18" t="n">
         <v>-2.5404</v>
@@ -1858,13 +1858,13 @@
         <v>9.7882</v>
       </c>
       <c r="S18" t="n">
-        <v>1.9401</v>
+        <v>2.443</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8613000000000001</v>
+        <v>-0.1087</v>
       </c>
       <c r="U18" t="n">
-        <v>2.8014</v>
+        <v>2.5517</v>
       </c>
       <c r="V18" t="n">
         <v>-3.0391</v>
@@ -1891,19 +1891,19 @@
         <v>34</v>
       </c>
       <c r="D19" t="n">
-        <v>232.0298</v>
+        <v>252.2380999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>200.2925</v>
+        <v>208.6565</v>
       </c>
       <c r="F19" t="n">
-        <v>31.7369</v>
+        <v>43.5823</v>
       </c>
       <c r="G19" t="n">
         <v>173.1204</v>
       </c>
       <c r="H19" t="n">
-        <v>99.10230000000001</v>
+        <v>99.1023</v>
       </c>
       <c r="I19" t="n">
         <v>74.01780000000001</v>
@@ -1912,7 +1912,7 @@
         <v>477.971</v>
       </c>
       <c r="K19" t="n">
-        <v>283.8781</v>
+        <v>283.8781000000001</v>
       </c>
       <c r="L19" t="n">
         <v>194.0929</v>
@@ -1933,16 +1933,16 @@
         <v>-452.9889</v>
       </c>
       <c r="R19" t="n">
-        <v>504.2058999999999</v>
+        <v>504.2059</v>
       </c>
       <c r="S19" t="n">
-        <v>38.2383</v>
+        <v>58.44759999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-23.26090000000001</v>
+        <v>-14.8988</v>
       </c>
       <c r="U19" t="n">
-        <v>61.50160000000001</v>
+        <v>73.3472</v>
       </c>
       <c r="V19" t="n">
         <v>-30.5462</v>
